--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486277_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486277_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1681</v>
+        <v>3.3649</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5796</v>
+        <v>3.2696</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5884</v>
+        <v>0.0953</v>
       </c>
       <c r="G2" t="n">
         <v>0.6661</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5242</v>
+        <v>0.721</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4747</v>
+        <v>0.1646</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0495</v>
+        <v>0.5564</v>
       </c>
       <c r="V2" t="n">
         <v>1.3252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3968</v>
+        <v>0.95</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6322</v>
+        <v>2.2163</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2354</v>
+        <v>-1.2662</v>
       </c>
       <c r="G3" t="n">
         <v>0.6045</v>
@@ -688,13 +688,13 @@
         <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6851</v>
+        <v>-0.1319</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.399</v>
+        <v>0.1851</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2861</v>
+        <v>-0.317</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0765</v>
+        <v>-0.1073</v>
       </c>
       <c r="E4" t="n">
         <v>0.2097</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2862</v>
+        <v>-0.317</v>
       </c>
       <c r="G4" t="n">
         <v>0.3618</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1131</v>
+        <v>-0.1439</v>
       </c>
       <c r="T4" t="n">
         <v>-0.137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0239</v>
+        <v>-0.0069</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7602</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2814</v>
+        <v>-0.2506</v>
       </c>
       <c r="E5" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2129</v>
+        <v>-0.1821</v>
       </c>
       <c r="G5" t="n">
         <v>-0.08450000000000001</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T5" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2983</v>
+        <v>-1.0899</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6847</v>
+        <v>0.2629</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.983</v>
+        <v>-1.3529</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6086</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5499</v>
+        <v>0.7583</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0227</v>
+        <v>0.6009</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5273</v>
+        <v>0.1574</v>
       </c>
       <c r="V6" t="n">
         <v>-0.152</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9677</v>
+        <v>-2.2411</v>
       </c>
       <c r="E7" t="n">
-        <v>0.274</v>
+        <v>0.9698</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2417</v>
+        <v>-3.2109</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3207</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5825</v>
+        <v>-0.8559</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1644</v>
+        <v>-0.4687</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4181</v>
+        <v>-0.3873</v>
       </c>
       <c r="V7" t="n">
         <v>0.4129</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1682</v>
+        <v>-2.5166</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5381</v>
+        <v>1.0356</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7064</v>
+        <v>-3.5522</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1309</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7553</v>
+        <v>-0.1036</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3389</v>
+        <v>0.1586</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4164</v>
+        <v>-0.2623</v>
       </c>
       <c r="V8" t="n">
         <v>-0.152</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.211</v>
+        <v>-2.7658</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7378</v>
+        <v>-2.6008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4732</v>
+        <v>-0.165</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7003</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6165</v>
+        <v>-0.1712</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4194</v>
+        <v>-0.2824</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1971</v>
+        <v>0.1111</v>
       </c>
       <c r="V9" t="n">
         <v>1.3684</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9343</v>
+        <v>-3.4078</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9503</v>
+        <v>-1.0971</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.984</v>
+        <v>-2.3107</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6811</v>
+        <v>-4.4231</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5325</v>
+        <v>-1.9162</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2136</v>
+        <v>-2.5069</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5072</v>
+        <v>-1.025</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4689</v>
+        <v>0.0611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>-1.0861</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1882</v>
+        <v>-3.3981</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0636</v>
+        <v>-1.9773</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2519</v>
+        <v>-1.4208</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5944</v>
+        <v>-0.1391</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8051</v>
+        <v>-0.0721</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2108</v>
+        <v>-0.067</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6725</v>
+        <v>-0.5857</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6725</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1095</v>
+        <v>-4.3514</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7063</v>
+        <v>-2.5524</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4032</v>
+        <v>-1.799</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4231</v>
+        <v>-0.6811</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9162</v>
+        <v>0.5325</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5069</v>
+        <v>-1.2136</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.025</v>
+        <v>0.5072</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0611</v>
+        <v>0.4689</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0861</v>
+        <v>0.0382</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3981</v>
+        <v>-1.1882</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9773</v>
+        <v>0.0636</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4208</v>
+        <v>-1.2519</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7401</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8408</v>
+        <v>0.1772</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6813</v>
+        <v>0.2031</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1595</v>
+        <v>-0.0258</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5857</v>
+        <v>-1.6725</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5857</v>
+        <v>-1.6725</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0491</v>
+        <v>-4.7455</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.695</v>
+        <v>-2.5147</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3541</v>
+        <v>-2.2308</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6207</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9933</v>
+        <v>-0.6898</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.548</v>
+        <v>-0.3677</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4454</v>
+        <v>-0.3221</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.5311</v>
+        <v>-17.1611</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.239599999999999</v>
+        <v>-0.8695999999999993</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.2917</v>
+        <v>-16.2915</v>
       </c>
       <c r="G13" t="n">
         <v>-12.9375</v>
@@ -1441,7 +1441,7 @@
         <v>-7.1278</v>
       </c>
       <c r="J13" t="n">
-        <v>5.902200000000001</v>
+        <v>5.9022</v>
       </c>
       <c r="K13" t="n">
         <v>3.591</v>
@@ -1468,16 +1468,16 @@
         <v>13.0504</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1151</v>
+        <v>-0.745</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.454</v>
+        <v>-0.08410000000000006</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6611999999999999</v>
+        <v>-0.6610999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2159000000000001</v>
+        <v>-0.2159000000000002</v>
       </c>
       <c r="W13" t="n">
         <v>9.625399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.287</v>
+        <v>5.8386</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3094</v>
+        <v>4.5271</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9776</v>
+        <v>1.3115</v>
       </c>
       <c r="G14" t="n">
         <v>4.8602</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.283</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1032</v>
+        <v>0.3209</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3718</v>
+        <v>-0.0379</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3427</v>
+        <v>5.0427</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8305</v>
+        <v>5.1658</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4879</v>
+        <v>-0.1231</v>
       </c>
       <c r="G15" t="n">
         <v>4.8253</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8752</v>
+        <v>-0.1751</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3869</v>
+        <v>-0.0517</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4883</v>
+        <v>-0.1235</v>
       </c>
       <c r="V15" t="n">
         <v>-1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2889</v>
+        <v>4.0023</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8271</v>
+        <v>4.3577</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4618</v>
+        <v>-0.3554</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7131</v>
+        <v>4.8857</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0735</v>
+        <v>1.0464</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7866</v>
+        <v>3.8393</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5188</v>
+        <v>4.6148</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5411</v>
+        <v>0.5022</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0599</v>
+        <v>4.1126</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8057</v>
+        <v>0.2708</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5324</v>
+        <v>0.5442</v>
       </c>
       <c r="O16" t="n">
         <v>-0.2733</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5551</v>
+        <v>-0.146</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4627</v>
+        <v>-0.2572</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0924</v>
+        <v>0.1111</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0207</v>
+        <v>-2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1507</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1633</v>
+        <v>3.5256</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0361</v>
+        <v>3.7066</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1272</v>
+        <v>-0.181</v>
       </c>
       <c r="G17" t="n">
         <v>1.8177</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0204</v>
+        <v>0.3827</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6044</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6249</v>
+        <v>0.3166</v>
       </c>
       <c r="V17" t="n">
         <v>1.3252</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0864</v>
+        <v>2.3693</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0224</v>
+        <v>0.3219</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9360000000000001</v>
+        <v>2.0474</v>
       </c>
       <c r="G18" t="n">
-        <v>4.8857</v>
+        <v>0.7981</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0464</v>
+        <v>1.2165</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8393</v>
+        <v>-0.4184</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6148</v>
+        <v>1.3059</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5022</v>
+        <v>1.1529</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1126</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2708</v>
+        <v>-0.5077</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5442</v>
+        <v>0.0636</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2733</v>
+        <v>-0.5714</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0618</v>
+        <v>0.1361</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5924</v>
+        <v>-0.2439</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4694</v>
+        <v>0.38</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2999</v>
+        <v>2.3409</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0984</v>
+        <v>2.1565</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2015</v>
+        <v>0.1844</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7981</v>
+        <v>1.7131</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2165</v>
+        <v>-1.0735</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4184</v>
+        <v>2.7866</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3059</v>
+        <v>2.5188</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1529</v>
+        <v>-0.5411</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>3.0599</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5077</v>
+        <v>-0.8057</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0636</v>
+        <v>-0.5324</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5714</v>
+        <v>-0.2733</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0667</v>
+        <v>0.6072</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>-0.2079</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5341</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.1507</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6149</v>
+        <v>0.9907</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5667</v>
+        <v>1.3431</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0483</v>
+        <v>-0.3524</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2602</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0703</v>
+        <v>0.4461</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3461</v>
+        <v>0.1226</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.3235</v>
       </c>
       <c r="V20" t="n">
         <v>0.9347</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5663</v>
+        <v>0.168</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8169</v>
+        <v>1.1463</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2506</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3465</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0003</v>
+        <v>0.6021</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1717</v>
+        <v>0.5011</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1714</v>
+        <v>0.1009</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>Y. MENCIA HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.525</v>
+        <v>-0.3676</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7798</v>
+        <v>-1.3819</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2548</v>
+        <v>1.0143</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4925</v>
+        <v>-0.8591</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2128</v>
+        <v>-0.4989</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2797</v>
+        <v>-0.3602</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1411</v>
+        <v>-0.7514</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1793</v>
+        <v>-0.1976</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0382</v>
+        <v>-0.5538</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3514</v>
+        <v>-0.1077</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0335</v>
+        <v>-0.3013</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.318</v>
+        <v>0.1936</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0327</v>
+        <v>0.274</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4711</v>
+        <v>0.4146</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5617</v>
+        <v>-0.1406</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y. MENCIA HERNANDEZ</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9637</v>
+        <v>-1.0452</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8289</v>
+        <v>-1.1151</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8653</v>
+        <v>0.0699</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8591</v>
+        <v>-0.4925</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4989</v>
+        <v>-0.2128</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3602</v>
+        <v>-0.2797</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7514</v>
+        <v>-0.1411</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1976</v>
+        <v>-0.1793</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5538</v>
+        <v>0.0382</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1077</v>
+        <v>-0.3514</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3013</v>
+        <v>-0.0335</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1936</v>
+        <v>-0.318</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3221</v>
+        <v>0.5125</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0324</v>
+        <v>0.1358</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2896</v>
+        <v>0.3767</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6297</v>
+        <v>-3.5892</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6071</v>
+        <v>-3.9365</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0226</v>
+        <v>0.3473</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0042</v>
@@ -2326,13 +2326,13 @@
         <v>1.9576</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1029</v>
+        <v>-0.0625</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8099</v>
+        <v>-0.1394</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.293</v>
+        <v>0.0769</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.531</v>
+        <v>19.2761</v>
       </c>
       <c r="E25" t="n">
-        <v>16.2917</v>
+        <v>16.2915</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2394</v>
+        <v>2.9846</v>
       </c>
       <c r="G25" t="n">
         <v>12.9376</v>
       </c>
       <c r="H25" t="n">
-        <v>5.809700000000002</v>
+        <v>5.809700000000001</v>
       </c>
       <c r="I25" t="n">
         <v>7.127899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>16.3129</v>
       </c>
       <c r="S25" t="n">
-        <v>2.1149</v>
+        <v>2.8601</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6612999999999999</v>
+        <v>0.6610000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4539</v>
+        <v>2.1987</v>
       </c>
       <c r="V25" t="n">
         <v>0.2159999999999996</v>
